--- a/data/trans_dic/IP09B02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,94; 90,83</t>
+          <t>42,44; 93,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,82; 95,0</t>
+          <t>55,07; 95,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 75,38</t>
+          <t>10,11; 72,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76,48; 100,0</t>
+          <t>77,46; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,12; 96,44</t>
+          <t>66,51; 96,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,63; 86,1</t>
+          <t>42,3; 84,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,82; 81,89</t>
+          <t>30,58; 82,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77,79; 100,0</t>
+          <t>78,94; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,44; 92,42</t>
+          <t>67,96; 92,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56,13; 84,16</t>
+          <t>58,2; 85,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,56; 70,16</t>
+          <t>29,67; 69,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,1; 98,49</t>
+          <t>84,24; 98,7</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,21; 91,5</t>
+          <t>57,91; 91,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,46; 71,93</t>
+          <t>44,51; 71,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 60,58</t>
+          <t>23,95; 59,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,55; 100,0</t>
+          <t>75,04; 98,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,52; 85,55</t>
+          <t>60,9; 87,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,91; 67,54</t>
+          <t>36,36; 63,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,62; 70,73</t>
+          <t>35,46; 71,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,84; 78,46</t>
+          <t>46,51; 78,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,83; 84,62</t>
+          <t>65,23; 86,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,47; 64,3</t>
+          <t>43,21; 64,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,69; 60,42</t>
+          <t>35,5; 60,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,98; 86,44</t>
+          <t>64,63; 86,38</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,15; 86,34</t>
+          <t>32,49; 86,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,87; 74,29</t>
+          <t>39,06; 73,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,94; 81,85</t>
+          <t>32,61; 84,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,59; 94,92</t>
+          <t>60,66; 95,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,69; 95,65</t>
+          <t>60,13; 95,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,63; 84,81</t>
+          <t>56,12; 83,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,78; 92,47</t>
+          <t>43,74; 92,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,44; 85,78</t>
+          <t>49,4; 85,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,29; 86,88</t>
+          <t>60,2; 88,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,5; 75,28</t>
+          <t>52,27; 74,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,01; 79,97</t>
+          <t>45,84; 82,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,69; 86,65</t>
+          <t>60,78; 86,09</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,44; 82,83</t>
+          <t>48,54; 82,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,65; 79,53</t>
+          <t>41,6; 78,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,3; 92,0</t>
+          <t>43,97; 93,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,52; 76,82</t>
+          <t>35,27; 74,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,07; 94,44</t>
+          <t>69,95; 94,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,28; 80,12</t>
+          <t>48,4; 80,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 70,81</t>
+          <t>21,72; 67,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,98; 84,13</t>
+          <t>54,9; 84,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,84; 86,14</t>
+          <t>65,1; 86,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53,43; 76,67</t>
+          <t>51,79; 75,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,99; 73,6</t>
+          <t>39,08; 73,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,62; 76,78</t>
+          <t>52,77; 77,46</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,04; 79,53</t>
+          <t>60,4; 80,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,97; 70,41</t>
+          <t>53,45; 71,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,66; 62,55</t>
+          <t>39,46; 64,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70,22; 88,39</t>
+          <t>70,86; 89,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,61; 87,96</t>
+          <t>75,03; 88,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,32; 70,98</t>
+          <t>54,88; 71,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,35; 66,85</t>
+          <t>42,5; 65,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,16; 83,51</t>
+          <t>64,66; 82,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,76; 83,16</t>
+          <t>71,64; 83,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,05</t>
+          <t>56,71; 68,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,34; 61,22</t>
+          <t>44,71; 61,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,55; 83,15</t>
+          <t>69,98; 82,88</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7016</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11213</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11171</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14825</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>22175</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>21843</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22207</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9020</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>33346</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4144; 9105</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7746; 13361</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>826; 5912</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9300; 12006</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11216; 16269</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6831; 13636</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2969; 8011</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>18891; 23931</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>18097; 24670</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17584; 25951</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5304; 12396</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>30275; 35470</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11834</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16091</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8191</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19596</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16167</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10627</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16396</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>32729</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32258</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18817</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>35992</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8701; 13742</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12375; 19760</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4693; 11686</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16029; 21043</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>16862; 24343</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11426; 19982</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7106; 14305</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12064; 20449</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>27861; 36766</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>25591; 38011</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>14071; 24033</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>30569; 40854</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10873</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5319</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12619</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17426</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6402</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14664</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>17554</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28299</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11722</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>26793</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2556; 6815</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7516; 14138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2938; 7621</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8802; 13808</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9239; 14646</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13843; 20676</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3967; 8418</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10353; 17990</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13988; 20519</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22949; 32876</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8287; 14858</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>21558; 30534</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15610</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13097</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7477</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8645</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18992</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17420</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>20213</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>34601</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30517</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13061</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>28858</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11121; 19011</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8789; 16651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4551; 9628</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5527; 11683</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15539; 20997</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>12608; 20974</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2742; 8475</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>15483; 23818</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>29377; 39159</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>24434; 35475</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8981; 16954</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>23154; 33985</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>39396</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>51274</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>24192</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>51540</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>73448</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>106727</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113281</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>52621</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>124989</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33568; 44653</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43961; 58425</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18596; 30253</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45028; 56624</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>61625; 72284</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53943; 70547</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21865; 33701</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>64030; 82179</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>98650; 114986</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>102383; 123457</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>44075; 60958</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>113774; 134739</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,44; 93,24</t>
+          <t>43,84; 93,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,07; 95,0</t>
+          <t>54,85; 90,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 72,37</t>
+          <t>9,52; 70,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,46; 100,0</t>
+          <t>74,65; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,51; 96,47</t>
+          <t>70,02; 96,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,3; 84,44</t>
+          <t>46,35; 86,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,58; 82,51</t>
+          <t>32,6; 82,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78,94; 100,0</t>
+          <t>76,99; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,96; 92,64</t>
+          <t>65,35; 91,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,2; 85,89</t>
+          <t>57,43; 85,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,67; 69,33</t>
+          <t>30,64; 71,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,24; 98,7</t>
+          <t>82,8; 98,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,91; 91,46</t>
+          <t>58,06; 91,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,51; 71,06</t>
+          <t>42,54; 72,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,95; 59,64</t>
+          <t>23,56; 59,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,04; 98,51</t>
+          <t>76,32; 98,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,9; 87,93</t>
+          <t>59,92; 87,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,36; 63,59</t>
+          <t>36,82; 66,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,46; 71,38</t>
+          <t>36,33; 73,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,51; 78,85</t>
+          <t>46,48; 77,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,23; 86,08</t>
+          <t>64,44; 84,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,21; 64,18</t>
+          <t>44,14; 64,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,5; 60,63</t>
+          <t>34,58; 59,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,63; 86,38</t>
+          <t>63,74; 87,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,49; 86,6</t>
+          <t>32,19; 85,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,06; 73,47</t>
+          <t>38,11; 75,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,61; 84,6</t>
+          <t>31,87; 84,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,66; 95,16</t>
+          <t>59,23; 94,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,13; 95,31</t>
+          <t>63,98; 95,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,12; 83,83</t>
+          <t>53,42; 83,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,74; 92,83</t>
+          <t>43,66; 92,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,4; 85,83</t>
+          <t>50,16; 85,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60,2; 88,31</t>
+          <t>59,56; 87,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,27; 74,87</t>
+          <t>51,42; 74,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,84; 82,19</t>
+          <t>46,86; 81,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,78; 86,09</t>
+          <t>60,15; 86,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,54; 82,97</t>
+          <t>48,52; 83,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,6; 78,81</t>
+          <t>45,48; 78,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,97; 93,03</t>
+          <t>44,32; 92,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,27; 74,54</t>
+          <t>32,22; 73,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,95; 94,52</t>
+          <t>70,47; 94,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,4; 80,52</t>
+          <t>50,56; 80,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,72; 67,11</t>
+          <t>21,44; 67,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,9; 84,45</t>
+          <t>55,9; 83,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,1; 86,78</t>
+          <t>64,5; 86,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,79; 75,2</t>
+          <t>53,18; 75,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,08; 73,78</t>
+          <t>38,77; 72,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,77; 77,46</t>
+          <t>51,99; 78,35</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,4; 80,35</t>
+          <t>60,24; 79,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,45; 71,04</t>
+          <t>54,06; 70,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,46; 64,2</t>
+          <t>39,33; 62,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70,86; 89,1</t>
+          <t>71,89; 89,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,03; 88,01</t>
+          <t>74,32; 88,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,88; 71,78</t>
+          <t>55,36; 70,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,5; 65,51</t>
+          <t>44,22; 66,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,66; 82,99</t>
+          <t>64,55; 83,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,64; 83,5</t>
+          <t>71,47; 82,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,71; 68,39</t>
+          <t>56,51; 67,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44,71; 61,84</t>
+          <t>46,0; 61,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,98; 82,88</t>
+          <t>70,47; 83,51</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4144; 9105</t>
+          <t>4281; 9120</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7746; 13361</t>
+          <t>7715; 12774</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>826; 5912</t>
+          <t>778; 5796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9300; 12006</t>
+          <t>8963; 12006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11216; 16269</t>
+          <t>11808; 16266</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6831; 13636</t>
+          <t>7486; 13896</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2969; 8011</t>
+          <t>3165; 8001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18891; 23931</t>
+          <t>18424; 23931</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18097; 24670</t>
+          <t>17402; 24260</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17584; 25951</t>
+          <t>17352; 25926</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5304; 12396</t>
+          <t>5477; 12805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30275; 35470</t>
+          <t>29755; 35489</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8701; 13742</t>
+          <t>8724; 13759</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12375; 19760</t>
+          <t>11829; 20055</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4693; 11686</t>
+          <t>4616; 11747</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16029; 21043</t>
+          <t>16301; 21064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16862; 24343</t>
+          <t>16589; 24208</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11426; 19982</t>
+          <t>11570; 20739</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7106; 14305</t>
+          <t>7280; 14719</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12064; 20449</t>
+          <t>12054; 20007</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27861; 36766</t>
+          <t>27523; 36194</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25591; 38011</t>
+          <t>26141; 37912</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14071; 24033</t>
+          <t>13708; 23554</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30569; 40854</t>
+          <t>30145; 41347</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2556; 6815</t>
+          <t>2533; 6729</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7516; 14138</t>
+          <t>7333; 14435</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2938; 7621</t>
+          <t>2871; 7599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8802; 13808</t>
+          <t>8594; 13767</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9239; 14646</t>
+          <t>9831; 14640</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13843; 20676</t>
+          <t>13175; 20638</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3967; 8418</t>
+          <t>3959; 8371</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10353; 17990</t>
+          <t>10513; 17888</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13988; 20519</t>
+          <t>13839; 20305</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22949; 32876</t>
+          <t>22579; 32891</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8287; 14858</t>
+          <t>8472; 14679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21558; 30534</t>
+          <t>21336; 30514</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11121; 19011</t>
+          <t>11118; 19111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8789; 16651</t>
+          <t>9608; 16583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4551; 9628</t>
+          <t>4587; 9587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5527; 11683</t>
+          <t>5049; 11573</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15539; 20997</t>
+          <t>15656; 20968</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12608; 20974</t>
+          <t>13169; 20941</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2742; 8475</t>
+          <t>2707; 8468</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15483; 23818</t>
+          <t>15767; 23640</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29377; 39159</t>
+          <t>29107; 38986</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24434; 35475</t>
+          <t>25088; 35622</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8981; 16954</t>
+          <t>8908; 16668</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23154; 33985</t>
+          <t>22811; 34378</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33568; 44653</t>
+          <t>33479; 44264</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43961; 58425</t>
+          <t>44459; 58200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18596; 30253</t>
+          <t>18533; 29516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45028; 56624</t>
+          <t>45687; 56596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61625; 72284</t>
+          <t>61042; 72400</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53943; 70547</t>
+          <t>54405; 69358</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21865; 33701</t>
+          <t>22748; 34242</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64030; 82179</t>
+          <t>63923; 82207</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98650; 114986</t>
+          <t>98413; 114016</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102383; 123457</t>
+          <t>102009; 122446</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44075; 60958</t>
+          <t>45337; 61043</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113774; 134739</t>
+          <t>114571; 135763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59,89%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>71,85%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>79,72%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>39,23%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,89%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,84; 93,39</t>
+          <t>70,12; 96,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,85; 90,82</t>
+          <t>45,63; 86,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 70,96</t>
+          <t>30,82; 81,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74,65; 100,0</t>
+          <t>76,44; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,02; 96,45</t>
+          <t>42,94; 90,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,35; 86,05</t>
+          <t>56,82; 95,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,6; 82,4</t>
+          <t>11,57; 75,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,99; 100,0</t>
+          <t>77,19; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,35; 91,1</t>
+          <t>66,44; 92,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,43; 85,81</t>
+          <t>56,13; 84,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,64; 71,62</t>
+          <t>31,56; 70,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,8; 98,75</t>
+          <t>83,2; 98,25</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51,45%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53,03%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62,85%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>78,76%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>57,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>41,8%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>51,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53,03%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,06; 91,57</t>
+          <t>60,52; 85,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,54; 72,12</t>
+          <t>36,91; 67,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,56; 59,95</t>
+          <t>32,62; 70,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,32; 98,62</t>
+          <t>43,74; 78,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,92; 87,44</t>
+          <t>58,21; 91,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,82; 66,0</t>
+          <t>41,46; 71,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,33; 73,44</t>
+          <t>24,91; 60,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,48; 77,14</t>
+          <t>71,56; 97,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,44; 84,74</t>
+          <t>63,83; 84,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,14; 64,01</t>
+          <t>43,47; 64,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,58; 59,43</t>
+          <t>33,69; 60,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,74; 87,42</t>
+          <t>61,81; 83,57</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82,12%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>70,6%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70,27%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>62,72%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>56,5%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>59,05%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83,59%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,6%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,19; 85,51</t>
+          <t>60,69; 95,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,11; 75,01</t>
+          <t>53,63; 84,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,87; 84,36</t>
+          <t>41,78; 92,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,23; 94,88</t>
+          <t>48,44; 86,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,98; 95,28</t>
+          <t>31,15; 86,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,42; 83,67</t>
+          <t>39,87; 74,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,66; 92,31</t>
+          <t>32,94; 81,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,16; 85,34</t>
+          <t>58,44; 95,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,56; 87,38</t>
+          <t>59,29; 86,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51,42; 74,91</t>
+          <t>52,5; 75,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,86; 81,2</t>
+          <t>46,01; 79,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,15; 86,03</t>
+          <t>60,64; 86,67</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44,22%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71,87%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>68,13%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>61,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>72,24%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>85,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,22%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,52; 83,41</t>
+          <t>70,07; 94,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,48; 78,49</t>
+          <t>50,28; 80,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,32; 92,63</t>
+          <t>22,25; 70,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,22; 73,84</t>
+          <t>54,88; 83,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,47; 94,39</t>
+          <t>48,44; 82,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,56; 80,4</t>
+          <t>41,65; 79,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,44; 67,05</t>
+          <t>42,3; 92,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55,9; 83,82</t>
+          <t>33,4; 76,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,5; 86,39</t>
+          <t>64,84; 86,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53,18; 75,51</t>
+          <t>53,43; 76,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,77; 72,54</t>
+          <t>37,99; 73,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,99; 78,35</t>
+          <t>52,06; 76,26</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>51,34%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>63,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,24; 79,65</t>
+          <t>74,61; 87,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,06; 70,77</t>
+          <t>55,32; 70,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,33; 62,64</t>
+          <t>43,35; 66,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,89; 89,06</t>
+          <t>65,36; 82,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,32; 88,15</t>
+          <t>59,04; 79,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,36; 70,57</t>
+          <t>52,97; 70,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,22; 66,56</t>
+          <t>39,66; 62,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,55; 83,01</t>
+          <t>69,21; 86,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,47; 82,8</t>
+          <t>71,76; 83,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,51; 67,83</t>
+          <t>56,39; 68,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,0; 61,93</t>
+          <t>45,34; 61,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,47; 83,51</t>
+          <t>69,61; 82,22</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14825</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19060</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7016</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>11213</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3205</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11171</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14825</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5815</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>30755</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4281; 9120</t>
+          <t>11825; 16263</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7715; 12774</t>
+          <t>7369; 13904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>778; 5796</t>
+          <t>2993; 7951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8963; 12006</t>
+          <t>15772; 20633</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11808; 16266</t>
+          <t>4193; 8870</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7486; 13896</t>
+          <t>7992; 13361</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3165; 8001</t>
+          <t>945; 6158</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18424; 23931</t>
+          <t>9657; 12511</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17402; 24260</t>
+          <t>17692; 24611</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17352; 25926</t>
+          <t>16958; 25429</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5477; 12805</t>
+          <t>5642; 12544</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29755; 35489</t>
+          <t>27577; 32562</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16167</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10627</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14648</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11834</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16091</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8191</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19596</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16167</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10627</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>29046</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8724; 13759</t>
+          <t>16755; 23686</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11829; 20055</t>
+          <t>11596; 21221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4616; 11747</t>
+          <t>6538; 14175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16301; 21064</t>
+          <t>10194; 18302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16589; 24208</t>
+          <t>8746; 13749</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11570; 20739</t>
+          <t>11529; 20001</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7280; 14719</t>
+          <t>4881; 11871</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12054; 20007</t>
+          <t>11555; 15802</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27523; 36194</t>
+          <t>27264; 36141</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26141; 37912</t>
+          <t>25746; 38084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13708; 23554</t>
+          <t>13354; 23948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30145; 41347</t>
+          <t>24388; 32974</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12619</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17426</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6402</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13955</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4935</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10873</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5319</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12130</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12619</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17426</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6402</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>26286</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2533; 6729</t>
+          <t>9326; 14698</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7333; 14435</t>
+          <t>13229; 20919</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2871; 7599</t>
+          <t>3789; 8385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8594; 13767</t>
+          <t>9619; 17224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9831; 14640</t>
+          <t>2451; 6794</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13175; 20638</t>
+          <t>7672; 14297</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3959; 8371</t>
+          <t>2967; 7373</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10513; 17888</t>
+          <t>8626; 14052</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13839; 20305</t>
+          <t>13776; 20187</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22579; 32891</t>
+          <t>23053; 33053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8472; 14679</t>
+          <t>8318; 14456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21336; 30514</t>
+          <t>20990; 30001</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18992</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17420</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18020</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15610</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13097</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7477</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8645</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18992</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17420</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5584</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>26438</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11118; 19111</t>
+          <t>15566; 20981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9608; 16583</t>
+          <t>13096; 20869</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4587; 9587</t>
+          <t>2810; 8943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5049; 11573</t>
+          <t>13760; 21017</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15656; 20968</t>
+          <t>11100; 18979</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13169; 20941</t>
+          <t>8800; 16802</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2707; 8468</t>
+          <t>4378; 9522</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15767; 23640</t>
+          <t>5232; 11915</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29107; 38986</t>
+          <t>29258; 38871</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25088; 35622</t>
+          <t>25204; 36169</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8908; 16668</t>
+          <t>8730; 16912</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22811; 34378</t>
+          <t>21208; 31067</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>65683</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>39396</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>51274</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>24192</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>67331</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62007</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>124989</t>
+          <t>112525</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33479; 44264</t>
+          <t>61277; 72241</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44459; 58200</t>
+          <t>54369; 69759</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18533; 29516</t>
+          <t>22300; 34394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45687; 56596</t>
+          <t>58089; 73728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61042; 72400</t>
+          <t>32809; 44199</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54405; 69358</t>
+          <t>43562; 57908</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22748; 34242</t>
+          <t>18689; 29474</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>63923; 82207</t>
+          <t>40889; 51248</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98413; 114016</t>
+          <t>98818; 114513</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102009; 122446</t>
+          <t>101791; 122853</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45337; 61043</t>
+          <t>44687; 60342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>114571; 135763</t>
+          <t>102983; 121641</t>
         </is>
       </c>
     </row>
